--- a/Supplementary Materials/S7.Evidence Tables.xlsx
+++ b/Supplementary Materials/S7.Evidence Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usr\Desktop\Supplementary Materials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\이유미\논문\2026년\HAI literacy\Framework\논문\HSS Comms\최종0728\S6.Extracted Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A7F493-1F09-4002-9619-2FAD5F9F18D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F74EF5-8BC8-4A2D-A4EE-60CAA4C90FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1E9297ED-9B27-4848-B12C-263506C361AE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E9297ED-9B27-4848-B12C-263506C361AE}"/>
   </bookViews>
   <sheets>
     <sheet name="S7.Evidence Tables" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -768,18 +771,18 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B1:Q273"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.69921875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18.19921875" style="6" customWidth="1"/>
-    <col min="3" max="5" width="10.69921875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="2.69921875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.69921875" style="3" customWidth="1"/>
-    <col min="8" max="10" width="10.69921875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="2.69921875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="23.69921875" style="3" customWidth="1"/>
-    <col min="13" max="17" width="10.69921875" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="8.796875" style="3"/>
+    <col min="1" max="1" width="2.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18.25" style="6" customWidth="1"/>
+    <col min="3" max="5" width="10.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="2.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.75" style="3" customWidth="1"/>
+    <col min="8" max="10" width="10.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="2.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="23.75" style="3" customWidth="1"/>
+    <col min="13" max="17" width="10.75" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="8.75" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17">
@@ -854,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
@@ -889,7 +892,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5">
         <v>5</v>

--- a/Supplementary Materials/S7.Evidence Tables.xlsx
+++ b/Supplementary Materials/S7.Evidence Tables.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\이유미\논문\2026년\HAI literacy\Framework\논문\HSS Comms\최종0728\S6.Extracted Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\연구프로젝트\2025_AI Literacy\July2026 리비전\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F74EF5-8BC8-4A2D-A4EE-60CAA4C90FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBFCE91-8BD1-406F-B976-F578E71E521B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E9297ED-9B27-4848-B12C-263506C361AE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="S7.Evidence Tables" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,28 +24,18 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
   <si>
-    <t>Count</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Duplications</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remains</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>UNESCO AI CFS (2024)</t>
   </si>
   <si>
     <t>Affective</t>
@@ -60,111 +47,99 @@
     <t>Cognitive</t>
   </si>
   <si>
+    <t>AI system design</t>
+  </si>
+  <si>
+    <t>AI techniques and applications</t>
+  </si>
+  <si>
+    <t>Ethics of AI</t>
+  </si>
+  <si>
     <t>Ethical</t>
   </si>
   <si>
-    <t>Sum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>Others</t>
   </si>
   <si>
     <t>Human-centred mindset</t>
   </si>
   <si>
-    <t>AI system design</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>ABCE Model (2024)</t>
   </si>
   <si>
-    <t>Ethics of AI</t>
+    <t>Table 2</t>
   </si>
   <si>
-    <t>AI techniques and applications</t>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Table 5</t>
+  </si>
+  <si>
+    <t>Remains</t>
+  </si>
+  <si>
+    <t>Table 4</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Duplications</t>
   </si>
   <si>
     <t>Others</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>sum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table 2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table 4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table 5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNESCO AI CFS (2024)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ABCE Model (2024)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>Sum</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="times news romans"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="times news romans"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="times news romans"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="times news romans"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="times news romans"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="times news romans"/>
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,12 +148,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -201,264 +182,489 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1" xr:uid="{6DAE9F32-B6A1-4D17-AB8F-5F080AEC1999}"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+  <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE5D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF94A5DF"/>
+          <bgColor rgb="FF94A5DF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF6182D6"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF6182D6"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <border>
+        <left/>
+        <right/>
+        <top style="medium">
+          <color rgb="FF6182D6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF6182D6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thick">
+          <color rgb="FFFFFFFF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thick">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD7DFF4"/>
+          <bgColor rgb="FFD7DFF4"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFFFFFFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFFFFFFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFFFFFFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFFFFFFF"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFFFFFFF"/>
+        </horizontal>
+      </border>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="45"/>
+      <tableStyleElement type="headerRow" dxfId="44"/>
+      <tableStyleElement type="totalRow" dxfId="43"/>
+      <tableStyleElement type="firstColumn" dxfId="42"/>
+      <tableStyleElement type="lastColumn" dxfId="41"/>
+      <tableStyleElement type="firstRowStripe" dxfId="40"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="39"/>
+    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" dxfId="38"/>
+      <tableStyleElement type="headerRow" dxfId="37"/>
+      <tableStyleElement type="totalRow" dxfId="36"/>
+      <tableStyleElement type="firstColumn" dxfId="35"/>
+      <tableStyleElement type="lastColumn" dxfId="34"/>
+      <tableStyleElement type="firstRowStripe" dxfId="33"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="32"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -681,21 +887,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -757,186 +963,192 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD52A4CF-983E-41B6-A882-6AEE9CD87AD0}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:Q273"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75"/>
+  <dimension ref="B1:R273"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="2.75" style="3" customWidth="1"/>
     <col min="2" max="2" width="18.25" style="6" customWidth="1"/>
-    <col min="3" max="5" width="10.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="2.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.75" style="3" customWidth="1"/>
-    <col min="8" max="10" width="10.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9" style="3" customWidth="1"/>
+    <col min="9" max="10" width="10.75" style="3" customWidth="1"/>
     <col min="11" max="11" width="2.75" style="3" customWidth="1"/>
     <col min="12" max="12" width="23.75" style="3" customWidth="1"/>
-    <col min="13" max="17" width="10.75" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="8.75" style="3"/>
+    <col min="13" max="18" width="7.9140625" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17">
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="2:18">
+      <c r="B1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="G1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="L1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+    </row>
+    <row r="3" spans="2:18" ht="23.9" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="G1" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="L1" s="14" t="s">
+      <c r="G3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-    </row>
-    <row r="3" spans="2:17">
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="4" spans="2:18">
+      <c r="B4" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17">
-      <c r="B4" s="4" t="s">
-        <v>3</v>
       </c>
       <c r="C4" s="5">
         <v>37</v>
       </c>
       <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="14">
+        <f>C4-D4</f>
+        <v>36</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="14">
+        <f>H4-I4</f>
+        <v>25</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+    </row>
+    <row r="5" spans="2:18">
+      <c r="B5" s="4" t="s">
         <v>2</v>
-      </c>
-      <c r="E4" s="5">
-        <v>36</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="10">
-        <v>43</v>
-      </c>
-      <c r="I4" s="10">
-        <v>1</v>
-      </c>
-      <c r="J4" s="10">
-        <v>42</v>
-      </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-    </row>
-    <row r="5" spans="2:17">
-      <c r="B5" s="4" t="s">
-        <v>4</v>
       </c>
       <c r="C5" s="5">
         <v>31</v>
       </c>
       <c r="D5" s="5">
+        <v>6</v>
+      </c>
+      <c r="E5" s="14">
+        <f t="shared" ref="E5:E9" si="0">C5-D5</f>
+        <v>25</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="5">
+      <c r="H5" s="5">
+        <v>90</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="14">
+        <f>H5-I5</f>
+        <v>85</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="15">
+        <v>3</v>
+      </c>
+      <c r="N5" s="15">
+        <v>3</v>
+      </c>
+      <c r="O5" s="15">
+        <v>13</v>
+      </c>
+      <c r="P5" s="15">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="14">
+        <f>SUM(M5:Q5)</f>
         <v>25</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="10">
-        <v>65</v>
-      </c>
-      <c r="I5" s="10">
-        <f t="shared" ref="I5:I8" si="0">H5-J5</f>
-        <v>16</v>
-      </c>
-      <c r="J5" s="10">
-        <v>49</v>
-      </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="10">
+    </row>
+    <row r="6" spans="2:18">
+      <c r="B6" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="N5" s="10">
-        <v>3</v>
-      </c>
-      <c r="O5" s="10">
-        <v>14</v>
-      </c>
-      <c r="P5" s="10">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>SUM(M5:P5)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17">
-      <c r="B6" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="C6" s="5">
         <v>141</v>
@@ -944,93 +1156,99 @@
       <c r="D6" s="5">
         <v>15</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="14">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="10">
-        <v>94</v>
-      </c>
-      <c r="I6" s="10">
-        <f t="shared" si="0"/>
+      <c r="G6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="5">
+        <v>59</v>
+      </c>
+      <c r="I6" s="5">
         <v>10</v>
       </c>
-      <c r="J6" s="10">
-        <v>84</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" s="10">
+      <c r="J6" s="14">
+        <f>H6-I6</f>
+        <v>49</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="15">
         <v>12</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="15">
         <v>8</v>
       </c>
-      <c r="O6" s="10">
-        <v>61</v>
-      </c>
-      <c r="P6" s="10">
+      <c r="O6" s="15">
+        <v>62</v>
+      </c>
+      <c r="P6" s="15">
         <v>3</v>
       </c>
-      <c r="Q6" s="10">
-        <f>SUM(M6:P6)</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17">
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
+      <c r="R6" s="14">
+        <f>SUM(M6:Q6)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18">
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5">
         <v>56</v>
       </c>
       <c r="D7" s="5">
+        <v>7</v>
+      </c>
+      <c r="E7" s="14">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="5">
+        <v>50</v>
+      </c>
+      <c r="I7" s="5">
+        <v>7</v>
+      </c>
+      <c r="J7" s="14">
+        <f>H7-I7</f>
+        <v>43</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="15">
         <v>8</v>
       </c>
-      <c r="E7" s="5">
-        <v>48</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="10">
-        <v>27</v>
-      </c>
-      <c r="I7" s="10">
-        <f t="shared" si="0"/>
+      <c r="N7" s="15">
         <v>1</v>
       </c>
-      <c r="J7" s="10">
-        <v>26</v>
-      </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="10">
+      <c r="O7" s="15">
+        <v>15</v>
+      </c>
+      <c r="P7" s="15">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="14">
+        <f>SUM(M7:Q7)</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="B8" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="N7" s="10">
-        <v>1</v>
-      </c>
-      <c r="O7" s="10">
-        <v>15</v>
-      </c>
-      <c r="P7" s="10">
-        <v>25</v>
-      </c>
-      <c r="Q7" s="10">
-        <f>SUM(M7:P7)</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17">
-      <c r="B8" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C8" s="5">
         <v>7</v>
@@ -1038,115 +1256,144 @@
       <c r="D8" s="5">
         <v>0</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="14">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="10">
+        <v>8</v>
+      </c>
+      <c r="H8" s="5">
+        <v>45</v>
+      </c>
+      <c r="I8" s="5">
+        <v>4</v>
+      </c>
+      <c r="J8" s="14">
+        <f>H8-I8</f>
+        <v>41</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="15">
+        <v>8</v>
+      </c>
+      <c r="N8" s="15">
+        <v>11</v>
+      </c>
+      <c r="O8" s="15">
+        <v>13</v>
+      </c>
+      <c r="P8" s="15">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" s="14">
+        <f>SUM(M8:Q8)</f>
         <v>43</v>
       </c>
-      <c r="I8" s="10">
+    </row>
+    <row r="9" spans="2:18">
+      <c r="B9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="13">
+        <v>272</v>
+      </c>
+      <c r="D9" s="13">
+        <f>SUM(D4:D8)</f>
+        <v>29</v>
+      </c>
+      <c r="E9" s="13">
         <f t="shared" si="0"/>
+        <v>243</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="13">
+        <f>SUM(H4:H8)</f>
+        <v>272</v>
+      </c>
+      <c r="I9" s="13">
+        <f>SUM(I4:I8)</f>
+        <v>29</v>
+      </c>
+      <c r="J9" s="13">
+        <f>SUM(J4:J8)</f>
+        <v>243</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="5">
+        <v>5</v>
+      </c>
+      <c r="N9" s="5">
         <v>2</v>
       </c>
-      <c r="J8" s="10">
+      <c r="O9" s="5">
+        <v>23</v>
+      </c>
+      <c r="P9" s="5">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>6</v>
+      </c>
+      <c r="R9" s="14">
+        <f>SUM(M9:Q9)</f>
         <v>41</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="10">
-        <v>8</v>
-      </c>
-      <c r="N8" s="10">
-        <v>11</v>
-      </c>
-      <c r="O8" s="10">
-        <v>13</v>
-      </c>
-      <c r="P8" s="10">
-        <v>11</v>
-      </c>
-      <c r="Q8" s="10">
-        <f>SUM(M8:P8)</f>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17">
-      <c r="B9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="5">
-        <v>272</v>
-      </c>
-      <c r="D9" s="5">
-        <f>SUM(D4:D8)</f>
-        <v>30</v>
-      </c>
-      <c r="E9" s="5">
-        <f>SUM(E4:E8)</f>
-        <v>242</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="10">
-        <v>272</v>
-      </c>
-      <c r="I9" s="10">
-        <f>SUM(I4:I8)</f>
-        <v>30</v>
-      </c>
-      <c r="J9" s="10">
-        <f>SUM(J4:J8)</f>
-        <v>242</v>
-      </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M9" s="10">
-        <f>SUM(M5:M8)</f>
-        <v>31</v>
-      </c>
-      <c r="N9" s="10">
-        <f>SUM(N5:N8)</f>
-        <v>23</v>
-      </c>
-      <c r="O9" s="10">
-        <f>SUM(O5:O8)</f>
-        <v>103</v>
-      </c>
-      <c r="P9" s="10">
-        <f>SUM(P5:P8)</f>
-        <v>44</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17">
+    </row>
+    <row r="10" spans="2:18">
       <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="2:17">
+      <c r="L10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="13">
+        <f>SUM(M5:M9)</f>
+        <v>36</v>
+      </c>
+      <c r="N10" s="13">
+        <f>SUM(N5:N9)</f>
+        <v>25</v>
+      </c>
+      <c r="O10" s="13">
+        <f>SUM(O5:O9)</f>
+        <v>126</v>
+      </c>
+      <c r="P10" s="13">
+        <f>SUM(P5:P9)</f>
+        <v>49</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>7</v>
+      </c>
+      <c r="R10" s="14">
+        <f>SUM(R5:R9)</f>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18">
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="2:17">
+    <row r="12" spans="2:18">
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="2:17">
+    <row r="13" spans="2:18">
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="2:17">
+    <row r="14" spans="2:18">
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="2:17">
+    <row r="15" spans="2:18">
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="2:17">
+    <row r="16" spans="2:18">
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="2:2">
@@ -1921,74 +2168,106 @@
       <c r="B273" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G4:J7">
+    <sortCondition ref="G4:G7"/>
+  </sortState>
+  <mergeCells count="9">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="L1:R1"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="Q3:Q4"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="23" priority="21">
+    <cfRule type="expression" dxfId="31" priority="33">
       <formula>#REF!="Ethical"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="30" priority="34">
       <formula>#REF!="Cognitive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="29" priority="35">
       <formula>#REF!="Behavioural"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24">
+    <cfRule type="expression" dxfId="28" priority="36">
       <formula>#REF!="Affective"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B9">
-    <cfRule type="expression" dxfId="19" priority="17">
+  <conditionalFormatting sqref="B5:B8">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>$C3="Ethical"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="26" priority="30">
       <formula>$C3="Cognitive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="25" priority="31">
       <formula>$C3="Behavioural"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20">
+    <cfRule type="expression" dxfId="24" priority="32">
       <formula>$C3="Affective"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274:B1000">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="23" priority="25">
       <formula>$C274="Ethical"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="22" priority="26">
       <formula>$C274="Cognitive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="21" priority="27">
       <formula>$C274="Behavioural"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16">
+    <cfRule type="expression" dxfId="20" priority="28">
       <formula>$C274="Affective"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G9">
-    <cfRule type="expression" dxfId="11" priority="9">
+  <conditionalFormatting sqref="G8">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>$C6="Ethical"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="18" priority="22">
       <formula>$C6="Cognitive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="17" priority="23">
       <formula>$C6="Behavioural"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="16" priority="24">
       <formula>$C6="Affective"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L9">
+  <conditionalFormatting sqref="L10">
+    <cfRule type="expression" dxfId="15" priority="9">
+      <formula>$C7="Ethical"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="10">
+      <formula>$C7="Cognitive"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>$C7="Behavioural"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>$C7="Affective"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:R3">
+    <cfRule type="expression" dxfId="11" priority="13">
+      <formula>$C2="Ethical"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="14">
+      <formula>$C2="Cognitive"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>$C2="Behavioural"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="16">
+      <formula>$C2="Affective"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
     <cfRule type="expression" dxfId="7" priority="5">
       <formula>$C6="Ethical"</formula>
     </cfRule>
@@ -2002,20 +2281,21 @@
       <formula>$C6="Affective"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:Q3">
+  <conditionalFormatting sqref="B9">
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$C2="Ethical"</formula>
+      <formula>$C6="Ethical"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$C2="Cognitive"</formula>
+      <formula>$C6="Cognitive"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$C2="Behavioural"</formula>
+      <formula>$C6="Behavioural"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>$C2="Affective"</formula>
+      <formula>$C6="Affective"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>